--- a/tournaments/kumpoo-2026/input/Draws Kumpoo Tervasulan Eliitti 2026.XLSX
+++ b/tournaments/kumpoo-2026/input/Draws Kumpoo Tervasulan Eliitti 2026.XLSX
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424">
   <si>
     <t>Kumpoo Tervasulan Eliitti 2026</t>
   </si>
@@ -301,82 +301,82 @@
     <t xml:space="preserve">Aapeli Pökkylä [1]  </t>
   </si>
   <si>
+    <t xml:space="preserve">Jimi Manninen  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikael Oilinki  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aapeli Pökkylä </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jimi Manninen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikael Oilinki </t>
+  </si>
+  <si>
+    <t>BS U17 - Group B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBC  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Korkeamäki [2]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juhana Paaso  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matti Isomaa  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Korkeamäki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juhana Paaso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matti Isomaa </t>
+  </si>
+  <si>
+    <t>BS U17 - Group C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aatos Pökkylä [3/4]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naitik Diwate  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Lenni Autio  </t>
   </si>
   <si>
-    <t xml:space="preserve">Mikael Oilinki  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aapeli Pökkylä </t>
+    <t xml:space="preserve">Naitik Diwate </t>
   </si>
   <si>
     <t xml:space="preserve">Lenni Autio </t>
   </si>
   <si>
-    <t xml:space="preserve">Mikael Oilinki </t>
-  </si>
-  <si>
-    <t>BS U17 - Group B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBC  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elis Korkeamäki [2]  </t>
+    <t>BS U17 - Group D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Jinu John [3/4]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luleå BMK  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hampus Hansson  </t>
   </si>
   <si>
     <t xml:space="preserve">Niilo Niskanen  </t>
   </si>
   <si>
-    <t xml:space="preserve">Naitik Diwate  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elis Korkeamäki </t>
+    <t xml:space="preserve">Hampus Hansson </t>
   </si>
   <si>
     <t xml:space="preserve">Niilo Niskanen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naitik Diwate </t>
-  </si>
-  <si>
-    <t>BS U17 - Group C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aatos Pökkylä [3/4]  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juhana Paaso  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jimi Manninen  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juhana Paaso </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jimi Manninen </t>
-  </si>
-  <si>
-    <t>BS U17 - Group D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luleå BMK  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hampus Hansson [3/4]  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Jinu John  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matti Isomaa  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hampus Hansson </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matti Isomaa </t>
   </si>
   <si>
     <t>MS 35-Main Draw</t>
@@ -643,142 +643,145 @@
     <t xml:space="preserve">Heikki Roivainen [1] </t>
   </si>
   <si>
+    <t xml:space="preserve">HPC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommi Salonpää </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YlTe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aapeli Pökkylä [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niklas Hukari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luleå BMK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eetu Hanhineva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeSu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iiro Romppainen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Korkeamäki [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 </t>
+  </si>
+  <si>
     <t xml:space="preserve">HBC </t>
   </si>
   <si>
-    <t xml:space="preserve">Bye 5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">YlTe </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aapeli Pökkylä [3/4] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eetu Hanhineva </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 </t>
+    <t xml:space="preserve">13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janne Haurinen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 </t>
   </si>
   <si>
     <t xml:space="preserve">SoMaSe </t>
   </si>
   <si>
-    <t xml:space="preserve">Janne Haurinen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeSu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iiro Romppainen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TU </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niklas Hukari </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 4 </t>
+    <t xml:space="preserve">15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaakko Hakala [2] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 </t>
+  </si>
+  <si>
+    <t>MD A-Main Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janne Haurinen [1] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marko Koivusaari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoang Nguyen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aki-Petteri Pokka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juha Heikkinen [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henri Kangas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aki Pirneskoski </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janne Julkunen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Pasanen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severi Myllymäki </t>
   </si>
   <si>
     <t xml:space="preserve">Jaakko Hakala [3/4] </t>
   </si>
   <si>
-    <t xml:space="preserve">12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommi Salonpää </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niklas Hobro [2] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luleå BMK </t>
-  </si>
-  <si>
-    <t>MD A-Main Draw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janne Haurinen [1] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marko Koivusaari </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aki Pirneskoski </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juha Heikkinen [3/4] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henri Kangas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoang Nguyen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aki-Petteri Pokka </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 7 </t>
+    <t xml:space="preserve">Lassi Lybeck </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESB </t>
   </si>
   <si>
     <t xml:space="preserve">Jukka-Pekka Kivistö </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severi Myllymäki </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lassi Lybeck </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESB </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janne Julkunen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Pasanen </t>
   </si>
   <si>
     <t xml:space="preserve">Aaro Romppainen [2] </t>
@@ -840,243 +843,243 @@
     <t xml:space="preserve">Pauli Alapukki [1] </t>
   </si>
   <si>
+    <t xml:space="preserve">Milo Stridsman </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KajSu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teemu Rantala [5/8] </t>
+  </si>
+  <si>
     <t xml:space="preserve">Jesse Nurmenniemi </t>
   </si>
   <si>
-    <t xml:space="preserve">Bye 9 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axel Lejon Öhrling [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KajSu </t>
+    <t xml:space="preserve">JeBa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walter Ekstrand [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuwan Withanage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matti Peitso [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axel Lejon Öhrling </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaakko Raasakka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klaki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma Lybeck </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaro Romppainen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joonas Huovila [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JySS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Pasanen [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anssi Isopahkala </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar Syk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aki-Petteri Pokka [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bye 10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Oikarinen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pihla Mäkelä [2] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVS </t>
+  </si>
+  <si>
+    <t>MD B-Main Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Korkeamäki [1] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMK Hoppet Haparanda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toni Kesti </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jouni Nikkeri </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Nurmenniemi [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matti Peitso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RVS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joonas Koskinen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harri Lukkarila </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aki Pirneskoski [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KäKa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timo Surakka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Hakala </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hannu Wärme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veetu Kyllönen [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilari Leskelä </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC Kokkola </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arttu Erkkilä </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samu Laitinen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janne Jyrkkä </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarkko Seppä </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vesa Lumme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu Siliämaa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henna Hukari [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tero Pökkylä </t>
   </si>
   <si>
     <t xml:space="preserve">Teemu Rantala </t>
   </si>
   <si>
-    <t xml:space="preserve">Nuwan Withanage </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TVS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pihla Mäkelä [3/4] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matti Peitso </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 11 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hampus Hansson [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaakko Raasakka </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JySS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Oikarinen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 8 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar Syk [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaro Romppainen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klaki </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emma Lybeck </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Pasanen [3/4] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anssi Isopahkala </t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walter Ekstrand [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JeBa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye 10 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milo Stridsman [2] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 </t>
-  </si>
-  <si>
-    <t>MD B-Main Draw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hampus Hansson [1] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milo Stridsman </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janne Jyrkkä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarkko Seppä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMK Hoppet Haparanda </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Hakala [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hannu Wärme </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RVS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joonas Koskinen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harri Lukkarila </t>
-  </si>
-  <si>
     <t xml:space="preserve">Olli Komulainen </t>
   </si>
   <si>
     <t xml:space="preserve">Pragnesh Prajapati </t>
   </si>
   <si>
-    <t xml:space="preserve">Jenni Lahti [3/4] </t>
+    <t xml:space="preserve">Nelly Määttä </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joonas Raasakka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janne Heikkilä [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teemu Karvonen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harri Huttula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalle Kouri </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenni Lahti [2] </t>
   </si>
   <si>
     <t xml:space="preserve">Pihla Mäkelä </t>
   </si>
   <si>
-    <t xml:space="preserve">Veetu Kyllönen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ilari Leskelä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toni Kesti </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jouni Nikkeri </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janne Heikkilä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KäKa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teemu Karvonen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harri Huttula [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalle Kouri </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nelly Määttä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henna Hukari </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tero Pökkylä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axel Lejon Öhrling [3/4] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar Syk </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joonas Raasakka </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC Kokkola </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arttu Erkkilä </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samu Laitinen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aki Pirneskoski [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timo Surakka </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vesa Lumme </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu Siliämaa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elis Korkeamäki [2] </t>
-  </si>
-  <si>
     <t>XD B-Main Draw</t>
   </si>
   <si>
@@ -1206,79 +1209,73 @@
     <t>MD C-Main Draw</t>
   </si>
   <si>
-    <t xml:space="preserve">Harri Huttula [1] </t>
-  </si>
-  <si>
     <t xml:space="preserve">Juha Seppälä </t>
   </si>
   <si>
     <t xml:space="preserve">Simo Tolonen </t>
   </si>
   <si>
+    <t xml:space="preserve">Aleksi Laurila </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harri Lukkarila [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arttu Erkkilä [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emilia Mattila </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanath K S </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Yang </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arttu Pirneskoski </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miika Surakka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jinu John </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajith Kutty </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joonas Koskinen [5/8] </t>
+  </si>
+  <si>
     <t xml:space="preserve">Abin Babu </t>
   </si>
   <si>
     <t xml:space="preserve">Shreeharsha Banavasi Venkatesh </t>
   </si>
   <si>
-    <t xml:space="preserve">Henna Hukari [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emilia Mattila </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyösti Alaruikka [3/4] </t>
+    <t xml:space="preserve">Janne Heikkilä [3/4] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veijo Höykinpuro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juha Alakulppi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anssi Isopahkala [5/8] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antti Ropponen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JuPy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyösti Alaruikka [2] </t>
   </si>
   <si>
     <t xml:space="preserve">Pragha Santhana </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veijo Höykinpuro </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janne Heikkilä [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arttu Pirneskoski </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miika Surakka </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JuPy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arttu Erkkilä [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juha Alakulppi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teemu Karvonen [3/4] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanath K S </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunny Yang </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleksi Laurila </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harri Lukkarila [5/8] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jinu John </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajith Kutty </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antti Ropponen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Hakala [2] </t>
   </si>
   <si>
     <t>WD C-Main Draw</t>
@@ -3111,7 +3108,7 @@
   <dimension ref="A1:G38"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="4" width="19" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
@@ -3278,7 +3275,7 @@
         <v>186</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -3304,7 +3301,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -3324,7 +3321,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -3367,10 +3364,10 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>3</v>
@@ -3396,7 +3393,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -3410,13 +3407,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -3456,13 +3453,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -3502,13 +3499,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -3551,10 +3548,10 @@
         <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>200</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>3</v>
@@ -3594,13 +3591,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -3640,13 +3637,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>3</v>
@@ -3672,7 +3669,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -3686,13 +3683,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C28" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -3781,7 +3778,7 @@
         <v>211</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>210</v>
@@ -3824,13 +3821,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>3</v>
@@ -3856,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>3</v>
@@ -3870,13 +3867,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>214</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -3997,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>218</v>
@@ -4020,7 +4017,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>219</v>
@@ -4089,10 +4086,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -4112,13 +4109,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>3</v>
@@ -4141,7 +4138,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -4161,7 +4158,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -4181,10 +4178,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -4204,13 +4201,13 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>222</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>221</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -4233,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -4247,13 +4244,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -4273,10 +4270,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -4293,16 +4290,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>224</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>3</v>
@@ -4339,7 +4336,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>3</v>
@@ -4365,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>226</v>
@@ -4388,10 +4385,10 @@
         <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>3</v>
@@ -4411,10 +4408,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>3</v>
@@ -4431,13 +4428,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -4477,16 +4474,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>205</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>3</v>
@@ -4503,13 +4500,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -4523,13 +4520,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -4578,7 +4575,7 @@
         <v>209</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>4</v>
@@ -4595,13 +4592,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -4618,10 +4615,10 @@
         <v>211</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -4661,16 +4658,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>3</v>
@@ -4687,13 +4684,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>3</v>
@@ -4707,13 +4704,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -4801,7 +4798,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
@@ -4837,10 +4834,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -4863,7 +4860,7 @@
         <v>141</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -4883,10 +4880,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -4906,10 +4903,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -4961,7 +4958,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -4993,7 +4990,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -5025,7 +5022,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -5057,7 +5054,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -5095,7 +5092,7 @@
   <dimension ref="A1:H70"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="4" width="23" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
@@ -5109,7 +5106,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -5128,7 +5125,7 @@
         <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>183</v>
@@ -5174,10 +5171,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>3</v>
@@ -5206,7 +5203,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -5278,10 +5275,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -5310,7 +5307,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -5333,7 +5330,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -5382,10 +5379,10 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>3</v>
@@ -5414,7 +5411,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -5431,13 +5428,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -5483,13 +5480,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -5535,10 +5532,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>253</v>
@@ -5639,13 +5636,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -5691,10 +5688,10 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>256</v>
@@ -5743,7 +5740,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
@@ -5798,7 +5795,7 @@
         <v>208</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>258</v>
@@ -5899,13 +5896,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -5951,13 +5948,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -6003,13 +6000,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>125</v>
+        <v>263</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -6055,13 +6052,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -6107,13 +6104,13 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>3</v>
@@ -6142,7 +6139,7 @@
         <v>3</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>3</v>
@@ -6159,13 +6156,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -6211,13 +6208,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -6263,13 +6260,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>272</v>
+        <v>111</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -6321,7 +6318,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>3</v>
@@ -6370,7 +6367,7 @@
         <v>275</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>274</v>
@@ -6422,10 +6419,10 @@
         <v>276</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -6471,13 +6468,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -6523,7 +6520,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
@@ -6558,7 +6555,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>3</v>
@@ -6575,13 +6572,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>280</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -6662,7 +6659,7 @@
         <v>3</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>4</v>
@@ -6679,13 +6676,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -6731,13 +6728,13 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>3</v>
@@ -6766,7 +6763,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -6783,13 +6780,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>288</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -6870,7 +6867,7 @@
   <dimension ref="A1:H70"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="23" customWidth="1"/>
+    <col min="3" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
@@ -6884,7 +6881,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3">
@@ -6903,7 +6900,7 @@
         <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>183</v>
@@ -6923,10 +6920,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -6949,13 +6946,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>291</v>
+        <v>89</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -6981,7 +6978,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>291</v>
+        <v>89</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -7027,10 +7024,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -7053,13 +7050,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>193</v>
+        <v>293</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>3</v>
@@ -7085,7 +7082,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -7108,7 +7105,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -7131,10 +7128,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>294</v>
+        <v>186</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -7157,13 +7154,13 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>294</v>
+        <v>186</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>296</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>295</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -7189,7 +7186,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -7206,13 +7203,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -7235,10 +7232,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -7258,13 +7255,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -7287,10 +7284,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -7310,13 +7307,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -7339,10 +7336,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -7365,13 +7362,13 @@
         <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>303</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>4</v>
@@ -7414,13 +7411,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -7443,7 +7440,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>304</v>
@@ -7466,10 +7463,10 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>305</v>
@@ -7518,7 +7515,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
@@ -7547,10 +7544,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>3</v>
@@ -7573,13 +7570,13 @@
         <v>208</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>4</v>
@@ -7605,7 +7602,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -7651,10 +7648,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>3</v>
@@ -7674,13 +7671,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -7703,10 +7700,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
@@ -7726,13 +7723,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -7755,10 +7752,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>308</v>
+        <v>111</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>3</v>
@@ -7778,13 +7775,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>309</v>
+        <v>197</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -7807,10 +7804,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>3</v>
@@ -7830,13 +7827,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>252</v>
+        <v>314</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -7882,16 +7879,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>3</v>
@@ -7911,13 +7908,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>3</v>
@@ -7934,13 +7931,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>294</v>
+        <v>189</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -7963,10 +7960,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>3</v>
@@ -7986,13 +7983,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -8015,10 +8012,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>3</v>
@@ -8038,13 +8035,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -8096,10 +8093,10 @@
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>3</v>
@@ -8119,13 +8116,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>317</v>
+        <v>195</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>3</v>
@@ -8145,10 +8142,10 @@
         <v>275</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>317</v>
+        <v>195</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>3</v>
@@ -8171,10 +8168,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>199</v>
+        <v>262</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>3</v>
@@ -8197,10 +8194,10 @@
         <v>276</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -8223,10 +8220,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>3</v>
@@ -8246,10 +8243,10 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>321</v>
@@ -8298,7 +8295,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
@@ -8327,7 +8324,7 @@
         <v>4</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>322</v>
@@ -8350,10 +8347,10 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>323</v>
@@ -8431,7 +8428,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>324</v>
@@ -8454,10 +8451,10 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>325</v>
@@ -8506,13 +8503,13 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>326</v>
@@ -8535,13 +8532,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>326</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>89</v>
+        <v>327</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -8558,13 +8555,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>89</v>
+        <v>327</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -8658,7 +8655,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3">
@@ -8711,10 +8708,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>3</v>
@@ -8734,7 +8731,7 @@
         <v>251</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>3</v>
@@ -8751,10 +8748,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>3</v>
@@ -8771,10 +8768,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -8791,10 +8788,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -8811,10 +8808,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -8831,10 +8828,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -8851,10 +8848,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -8871,10 +8868,10 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>3</v>
@@ -8891,10 +8888,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>3</v>
@@ -8908,13 +8905,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -8931,10 +8928,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -8948,13 +8945,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -8971,10 +8968,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -8988,13 +8985,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -9071,7 +9068,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3">
@@ -9090,7 +9087,7 @@
         <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>183</v>
@@ -9136,10 +9133,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>3</v>
@@ -9168,7 +9165,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -9240,10 +9237,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -9292,10 +9289,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -9344,10 +9341,10 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>3</v>
@@ -9376,7 +9373,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -9393,13 +9390,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -9445,13 +9442,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -9497,13 +9494,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -9552,10 +9549,10 @@
         <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>3</v>
@@ -9584,7 +9581,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>4</v>
@@ -9601,13 +9598,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -9653,13 +9650,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>3</v>
@@ -9705,13 +9702,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -9760,10 +9757,10 @@
         <v>208</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>3</v>
@@ -9812,10 +9809,10 @@
         <v>211</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -9861,13 +9858,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -9913,13 +9910,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -9965,10 +9962,10 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>127</v>
@@ -10017,13 +10014,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -10069,10 +10066,10 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>70</v>
@@ -10121,13 +10118,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -10173,13 +10170,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -10225,13 +10222,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -10283,7 +10280,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>3</v>
@@ -10312,7 +10309,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>3</v>
@@ -10332,10 +10329,10 @@
         <v>275</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>3</v>
@@ -10384,10 +10381,10 @@
         <v>276</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -10433,13 +10430,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -10485,7 +10482,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
@@ -10520,7 +10517,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>3</v>
@@ -10537,13 +10534,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -10592,10 +10589,10 @@
         <v>283</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>3</v>
@@ -10641,13 +10638,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -10693,13 +10690,13 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>3</v>
@@ -10728,7 +10725,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -10745,13 +10742,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -11442,7 +11439,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3">
@@ -11478,10 +11475,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -11504,7 +11501,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -11527,7 +11524,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -11547,10 +11544,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -11602,7 +11599,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -11634,7 +11631,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -11666,7 +11663,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -11698,7 +11695,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -11737,7 +11734,7 @@
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
@@ -11751,7 +11748,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -11770,7 +11767,7 @@
         <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>183</v>
@@ -11790,10 +11787,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -11816,13 +11813,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -11848,7 +11845,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -11946,10 +11943,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -11972,10 +11969,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -11998,10 +11995,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>202</v>
+        <v>298</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -12024,13 +12021,13 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>298</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>376</v>
+        <v>313</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -12056,7 +12053,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>376</v>
+        <v>313</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -12073,13 +12070,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -12102,10 +12099,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -12125,13 +12122,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -12154,10 +12151,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -12177,13 +12174,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -12206,10 +12203,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -12232,13 +12229,13 @@
         <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>4</v>
@@ -12264,7 +12261,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>4</v>
@@ -12281,13 +12278,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -12310,10 +12307,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>297</v>
+        <v>201</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>3</v>
@@ -12333,13 +12330,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>297</v>
+        <v>201</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>3</v>
@@ -12362,10 +12359,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>379</v>
+        <v>304</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>3</v>
@@ -12385,13 +12382,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>104</v>
+        <v>305</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -12414,10 +12411,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>380</v>
+        <v>315</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>3</v>
@@ -12440,10 +12437,10 @@
         <v>208</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>60</v>
+        <v>376</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>3</v>
@@ -12466,10 +12463,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>3</v>
@@ -12492,10 +12489,10 @@
         <v>211</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -12518,10 +12515,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>351</v>
+        <v>201</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>3</v>
@@ -12541,13 +12538,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -12570,10 +12567,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
@@ -12593,13 +12590,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -12622,10 +12619,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>335</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>3</v>
@@ -12645,13 +12642,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>383</v>
+        <v>201</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -12674,10 +12671,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>99</v>
+        <v>381</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>3</v>
@@ -12697,13 +12694,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -12726,10 +12723,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>3</v>
@@ -12749,13 +12746,13 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>3</v>
@@ -12778,10 +12775,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
@@ -12801,13 +12798,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -12830,10 +12827,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>3</v>
@@ -12853,13 +12850,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -12882,10 +12879,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>3</v>
@@ -12905,13 +12902,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -12963,7 +12960,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>386</v>
@@ -12986,13 +12983,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>386</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>323</v>
+        <v>60</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>3</v>
@@ -13012,10 +13009,10 @@
         <v>275</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>323</v>
+        <v>60</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>3</v>
@@ -13038,10 +13035,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>3</v>
@@ -13064,10 +13061,10 @@
         <v>276</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>337</v>
+        <v>98</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -13090,10 +13087,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>3</v>
@@ -13113,13 +13110,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -13142,10 +13139,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>3</v>
@@ -13165,13 +13162,13 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>389</v>
+        <v>325</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>3</v>
@@ -13194,10 +13191,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>297</v>
+        <v>186</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>3</v>
@@ -13217,13 +13214,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>297</v>
+        <v>201</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -13246,10 +13243,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>3</v>
@@ -13272,10 +13269,10 @@
         <v>283</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>3</v>
@@ -13298,10 +13295,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>278</v>
+        <v>336</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>3</v>
@@ -13321,13 +13318,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>199</v>
+        <v>391</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -13373,16 +13370,16 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>3</v>
@@ -13402,13 +13399,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>294</v>
+        <v>201</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>296</v>
+        <v>393</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -13425,13 +13422,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>201</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>296</v>
+        <v>393</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -13527,7 +13524,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3">
@@ -13566,10 +13563,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>397</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -13595,7 +13592,7 @@
         <v>132</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -13621,7 +13618,7 @@
         <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -13644,10 +13641,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>116</v>
@@ -13673,7 +13670,7 @@
         <v>134</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>117</v>
@@ -13728,7 +13725,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -13760,7 +13757,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -13792,7 +13789,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -13824,7 +13821,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>36</v>
@@ -13856,7 +13853,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
@@ -13908,7 +13905,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
@@ -13944,10 +13941,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -13967,13 +13964,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -13996,7 +13993,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -14036,10 +14033,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -14059,13 +14056,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>3</v>
@@ -14088,7 +14085,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -14108,7 +14105,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -14128,10 +14125,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -14151,13 +14148,13 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -14180,7 +14177,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -14194,13 +14191,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -14220,10 +14217,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>415</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -14240,13 +14237,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -14266,10 +14263,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -14286,13 +14283,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -14312,10 +14309,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -14335,10 +14332,10 @@
         <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>3</v>
@@ -14358,10 +14355,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>3</v>
@@ -14378,13 +14375,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -14424,16 +14421,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>205</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>3</v>
@@ -14450,13 +14447,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>421</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>422</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -14470,13 +14467,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>421</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>422</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -14525,7 +14522,7 @@
         <v>209</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>4</v>
@@ -14542,13 +14539,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -14565,10 +14562,10 @@
         <v>211</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -14608,16 +14605,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>3</v>
@@ -14634,13 +14631,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>423</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>424</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>3</v>
@@ -14654,13 +14651,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -16043,7 +16040,7 @@
   <dimension ref="A1:J42"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="8" width="3" customWidth="1"/>
@@ -16116,7 +16113,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>87</v>
@@ -16329,7 +16326,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>95</v>
@@ -16349,7 +16346,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>96</v>
@@ -16562,7 +16559,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>103</v>
@@ -16735,10 +16732,10 @@
         <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>107</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>3</v>
@@ -16755,7 +16752,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>109</v>
@@ -16827,7 +16824,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>36</v>
@@ -16859,7 +16856,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>36</v>
@@ -17035,7 +17032,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>120</v>
@@ -18103,13 +18100,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1DD35E7-5E3F-4E53-B114-61A496AAD2CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A998A2A8-F1B1-4026-9B6E-D2D31CC13EB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D08D31B-2891-4993-A48D-A6976DE860DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4D43B3-8AE9-424B-9AA3-76ACECCF21C4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FF5446-91EB-4A8D-B0D4-8C2209FBE099}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44C02B44-A968-4A99-AB20-0E835C0AF58A}"/>
 </file>
--- a/tournaments/kumpoo-2026/input/Draws Kumpoo Tervasulan Eliitti 2026.XLSX
+++ b/tournaments/kumpoo-2026/input/Draws Kumpoo Tervasulan Eliitti 2026.XLSX
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421">
   <si>
     <t>Kumpoo Tervasulan Eliitti 2026</t>
   </si>
@@ -244,12 +244,6 @@
     <t xml:space="preserve">Senuka Weeraddana  </t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bye  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Jonathan Jinu John </t>
   </si>
   <si>
@@ -257,9 +251,6 @@
   </si>
   <si>
     <t xml:space="preserve">Senuka Weeraddana </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4  </t>
   </si>
   <si>
     <t>BS U15 - Group C</t>
@@ -2195,7 +2186,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
@@ -2231,10 +2222,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -2254,10 +2245,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -2277,10 +2268,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -2300,10 +2291,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -2355,7 +2346,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -2387,7 +2378,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -2419,7 +2410,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -2451,7 +2442,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -2505,7 +2496,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
@@ -2541,10 +2532,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -2564,10 +2555,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -2587,10 +2578,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -2610,10 +2601,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -2665,7 +2656,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -2697,7 +2688,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -2729,7 +2720,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -2761,7 +2752,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -2814,7 +2805,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -2850,10 +2841,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -2873,10 +2864,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -2896,10 +2887,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -2919,10 +2910,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -2974,7 +2965,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -3006,7 +2997,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -3038,7 +3029,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -3070,7 +3061,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -3121,7 +3112,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
@@ -3137,10 +3128,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>6</v>
@@ -3180,10 +3171,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>3</v>
@@ -3209,7 +3200,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -3272,10 +3263,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -3301,7 +3292,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -3321,7 +3312,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -3361,13 +3352,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>3</v>
@@ -3393,7 +3384,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -3407,13 +3398,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -3453,13 +3444,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -3499,13 +3490,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -3545,13 +3536,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>3</v>
@@ -3591,13 +3582,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -3637,13 +3628,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>3</v>
@@ -3669,7 +3660,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -3683,13 +3674,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -3729,13 +3720,13 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>3</v>
@@ -3761,7 +3752,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -3775,13 +3766,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -3821,13 +3812,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>3</v>
@@ -3853,7 +3844,7 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>3</v>
@@ -3867,13 +3858,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -3958,7 +3949,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -3974,10 +3965,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>6</v>
@@ -3994,10 +3985,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -4017,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -4046,7 +4037,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -4086,10 +4077,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -4109,13 +4100,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>3</v>
@@ -4138,7 +4129,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -4158,7 +4149,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -4178,10 +4169,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -4198,16 +4189,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -4230,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -4244,13 +4235,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -4270,10 +4261,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -4290,16 +4281,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>3</v>
@@ -4322,7 +4313,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>3</v>
@@ -4336,13 +4327,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -4362,10 +4353,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -4382,13 +4373,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>3</v>
@@ -4408,10 +4399,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>3</v>
@@ -4428,13 +4419,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -4474,16 +4465,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>3</v>
@@ -4500,13 +4491,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -4520,13 +4511,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -4566,16 +4557,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>4</v>
@@ -4592,13 +4583,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -4612,13 +4603,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -4658,16 +4649,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>3</v>
@@ -4684,13 +4675,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>3</v>
@@ -4704,13 +4695,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -4798,7 +4789,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3">
@@ -4834,10 +4825,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -4857,10 +4848,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -4880,10 +4871,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -4903,10 +4894,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -4958,7 +4949,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -4990,7 +4981,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -5022,7 +5013,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -5054,7 +5045,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -5106,7 +5097,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
@@ -5122,13 +5113,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
@@ -5171,10 +5162,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>3</v>
@@ -5203,7 +5194,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -5275,10 +5266,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -5307,7 +5298,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -5330,7 +5321,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -5376,13 +5367,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>3</v>
@@ -5411,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -5428,13 +5419,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -5480,13 +5471,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -5532,13 +5523,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -5584,13 +5575,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>3</v>
@@ -5619,7 +5610,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>4</v>
@@ -5636,13 +5627,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -5688,13 +5679,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>3</v>
@@ -5723,7 +5714,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -5740,13 +5731,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -5792,13 +5783,13 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>3</v>
@@ -5827,7 +5818,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -5844,13 +5835,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -5896,13 +5887,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -5948,13 +5939,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -6000,13 +5991,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -6052,13 +6043,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -6104,13 +6095,13 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>3</v>
@@ -6139,7 +6130,7 @@
         <v>3</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>3</v>
@@ -6156,13 +6147,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -6208,13 +6199,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -6260,13 +6251,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -6312,13 +6303,13 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>3</v>
@@ -6347,7 +6338,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>3</v>
@@ -6364,13 +6355,13 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>3</v>
@@ -6416,13 +6407,13 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -6468,13 +6459,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -6520,13 +6511,13 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>3</v>
@@ -6555,7 +6546,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>3</v>
@@ -6572,13 +6563,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -6624,13 +6615,13 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>3</v>
@@ -6659,7 +6650,7 @@
         <v>3</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>4</v>
@@ -6676,13 +6667,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -6728,13 +6719,13 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>3</v>
@@ -6763,7 +6754,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -6780,13 +6771,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -6881,7 +6872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3">
@@ -6897,13 +6888,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
@@ -6920,10 +6911,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -6946,13 +6937,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -6978,7 +6969,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -7024,10 +7015,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -7050,13 +7041,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>3</v>
@@ -7082,7 +7073,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -7105,7 +7096,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -7128,10 +7119,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -7151,16 +7142,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -7186,7 +7177,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -7203,13 +7194,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -7232,10 +7223,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -7255,13 +7246,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -7284,10 +7275,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -7307,13 +7298,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -7336,10 +7327,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -7359,16 +7350,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>4</v>
@@ -7394,7 +7385,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>4</v>
@@ -7411,13 +7402,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -7440,10 +7431,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>3</v>
@@ -7463,16 +7454,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>3</v>
@@ -7498,7 +7489,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -7515,13 +7506,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -7544,10 +7535,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>3</v>
@@ -7567,16 +7558,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>4</v>
@@ -7602,7 +7593,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -7619,13 +7610,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -7648,10 +7639,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>3</v>
@@ -7671,13 +7662,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -7700,10 +7691,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
@@ -7723,13 +7714,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -7752,10 +7743,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>3</v>
@@ -7775,13 +7766,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -7804,10 +7795,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>3</v>
@@ -7827,13 +7818,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -7879,16 +7870,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>3</v>
@@ -7908,13 +7899,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>3</v>
@@ -7931,13 +7922,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -7960,10 +7951,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>3</v>
@@ -7983,13 +7974,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -8012,10 +8003,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>3</v>
@@ -8035,13 +8026,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -8087,16 +8078,16 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>3</v>
@@ -8116,13 +8107,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>3</v>
@@ -8139,13 +8130,13 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>3</v>
@@ -8168,10 +8159,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>3</v>
@@ -8191,13 +8182,13 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -8220,10 +8211,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>3</v>
@@ -8243,13 +8234,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -8295,16 +8286,16 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>3</v>
@@ -8324,13 +8315,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>3</v>
@@ -8347,13 +8338,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -8399,16 +8390,16 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>4</v>
@@ -8428,13 +8419,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>4</v>
@@ -8451,13 +8442,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -8503,16 +8494,16 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>3</v>
@@ -8532,13 +8523,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -8555,13 +8546,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -8655,7 +8646,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3">
@@ -8671,7 +8662,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>6</v>
@@ -8688,10 +8679,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -8708,10 +8699,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>3</v>
@@ -8728,10 +8719,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>3</v>
@@ -8748,10 +8739,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>3</v>
@@ -8768,10 +8759,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -8788,10 +8779,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -8808,10 +8799,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -8828,10 +8819,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -8848,10 +8839,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -8865,13 +8856,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>3</v>
@@ -8888,10 +8879,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>3</v>
@@ -8905,13 +8896,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C16" s="13" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -8928,10 +8919,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -8945,13 +8936,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -8968,10 +8959,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -8985,13 +8976,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -9068,7 +9059,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3">
@@ -9084,13 +9075,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
@@ -9133,10 +9124,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>3</v>
@@ -9165,7 +9156,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -9237,10 +9228,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -9289,10 +9280,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -9338,13 +9329,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>3</v>
@@ -9373,7 +9364,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -9390,13 +9381,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -9442,13 +9433,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -9494,13 +9485,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -9546,13 +9537,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>3</v>
@@ -9581,7 +9572,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>4</v>
@@ -9598,13 +9589,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -9650,13 +9641,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>3</v>
@@ -9702,13 +9693,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -9754,13 +9745,13 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>3</v>
@@ -9806,13 +9797,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -9858,13 +9849,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -9910,13 +9901,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -9962,13 +9953,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -10014,13 +10005,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -10066,13 +10057,13 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>3</v>
@@ -10118,13 +10109,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -10170,13 +10161,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -10222,13 +10213,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -10274,13 +10265,13 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>3</v>
@@ -10309,7 +10300,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>3</v>
@@ -10326,13 +10317,13 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>3</v>
@@ -10378,13 +10369,13 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -10430,13 +10421,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -10482,13 +10473,13 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>3</v>
@@ -10517,7 +10508,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>3</v>
@@ -10534,13 +10525,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -10586,13 +10577,13 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>3</v>
@@ -10638,13 +10629,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -10690,13 +10681,13 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>3</v>
@@ -10725,7 +10716,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -10742,13 +10733,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -11439,7 +11430,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3">
@@ -11475,10 +11466,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -11501,7 +11492,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -11524,7 +11515,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
@@ -11544,10 +11535,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -11599,7 +11590,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -11631,7 +11622,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -11663,7 +11654,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -11695,7 +11686,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -11748,7 +11739,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -11764,13 +11755,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
@@ -11787,10 +11778,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -11813,13 +11804,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -11845,7 +11836,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -11891,10 +11882,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -11917,10 +11908,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>3</v>
@@ -11943,10 +11934,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -11969,10 +11960,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -11995,10 +11986,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -12018,16 +12009,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -12053,7 +12044,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -12070,13 +12061,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -12099,10 +12090,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -12122,13 +12113,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -12151,10 +12142,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -12174,13 +12165,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -12203,10 +12194,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -12226,16 +12217,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>4</v>
@@ -12261,7 +12252,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>4</v>
@@ -12278,13 +12269,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -12307,10 +12298,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>3</v>
@@ -12330,13 +12321,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>3</v>
@@ -12359,10 +12350,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>3</v>
@@ -12382,13 +12373,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -12411,10 +12402,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>3</v>
@@ -12434,13 +12425,13 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>3</v>
@@ -12463,10 +12454,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>3</v>
@@ -12486,13 +12477,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -12515,10 +12506,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>3</v>
@@ -12538,13 +12529,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>3</v>
@@ -12567,10 +12558,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
@@ -12590,13 +12581,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -12619,10 +12610,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>3</v>
@@ -12642,13 +12633,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>3</v>
@@ -12671,10 +12662,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>3</v>
@@ -12694,13 +12685,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>3</v>
@@ -12723,10 +12714,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>3</v>
@@ -12746,13 +12737,13 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>3</v>
@@ -12775,10 +12766,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
@@ -12798,13 +12789,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>3</v>
@@ -12827,10 +12818,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>3</v>
@@ -12850,13 +12841,13 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>3</v>
@@ -12879,10 +12870,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>3</v>
@@ -12902,13 +12893,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>3</v>
@@ -12954,16 +12945,16 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>3</v>
@@ -12983,10 +12974,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>60</v>
@@ -13006,10 +12997,10 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>60</v>
@@ -13035,10 +13026,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>3</v>
@@ -13058,13 +13049,13 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>3</v>
@@ -13087,10 +13078,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>3</v>
@@ -13110,13 +13101,13 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>3</v>
@@ -13139,10 +13130,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>3</v>
@@ -13162,13 +13153,13 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>3</v>
@@ -13191,10 +13182,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>3</v>
@@ -13214,13 +13205,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>3</v>
@@ -13243,10 +13234,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>3</v>
@@ -13266,13 +13257,13 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>3</v>
@@ -13295,10 +13286,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>3</v>
@@ -13318,13 +13309,13 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>3</v>
@@ -13370,16 +13361,16 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>3</v>
@@ -13399,13 +13390,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>3</v>
@@ -13422,13 +13413,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>3</v>
@@ -13524,7 +13515,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -13555,7 +13546,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -13563,10 +13554,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -13578,10 +13569,10 @@
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -13589,10 +13580,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -13601,10 +13592,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>23</v>
@@ -13615,16 +13606,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>3</v>
@@ -13641,16 +13632,16 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
@@ -13664,16 +13655,16 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>23</v>
@@ -13725,7 +13716,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -13757,7 +13748,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -13789,7 +13780,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -13821,7 +13812,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>36</v>
@@ -13853,7 +13844,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
@@ -13905,7 +13896,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3">
@@ -13921,10 +13912,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>6</v>
@@ -13941,10 +13932,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -13964,13 +13955,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>4</v>
@@ -13993,7 +13984,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -14033,10 +14024,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -14056,13 +14047,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>3</v>
@@ -14085,7 +14076,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>3</v>
@@ -14105,7 +14096,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>3</v>
@@ -14125,10 +14116,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -14145,16 +14136,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -14177,7 +14168,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
@@ -14191,13 +14182,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -14217,10 +14208,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -14237,13 +14228,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>3</v>
@@ -14263,10 +14254,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -14283,13 +14274,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>3</v>
@@ -14309,10 +14300,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>3</v>
@@ -14329,13 +14320,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>3</v>
@@ -14355,10 +14346,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>3</v>
@@ -14375,13 +14366,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>3</v>
@@ -14421,16 +14412,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>3</v>
@@ -14447,13 +14438,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>3</v>
@@ -14467,13 +14458,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>3</v>
@@ -14513,16 +14504,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>4</v>
@@ -14539,13 +14530,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>4</v>
@@ -14559,13 +14550,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>3</v>
@@ -14605,16 +14596,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>3</v>
@@ -14631,13 +14622,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>3</v>
@@ -14651,13 +14642,13 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>3</v>
@@ -14944,7 +14935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J36"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
@@ -15275,9 +15266,6 @@
       <c r="F17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
@@ -15298,9 +15286,6 @@
       <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
@@ -15321,9 +15306,6 @@
       <c r="F19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
@@ -15344,63 +15326,69 @@
       <c r="F20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>3</v>
+      <c r="C22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -15408,7 +15396,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>36</v>
@@ -15440,7 +15428,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>36</v>
@@ -15467,220 +15455,220 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="5" t="s">
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>15</v>
+      <c r="D29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>75</v>
+        <v>26</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>3</v>
+      <c r="C34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -15688,7 +15676,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>36</v>
@@ -15720,7 +15708,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>36</v>
@@ -15744,70 +15732,6 @@
         <v>37</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J38" s="5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -15834,7 +15758,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -15918,7 +15842,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>3</v>
@@ -16055,7 +15979,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -16065,7 +15989,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -16096,7 +16020,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -16116,7 +16040,7 @@
         <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -16136,7 +16060,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>22</v>
@@ -16185,7 +16109,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -16217,7 +16141,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -16249,7 +16173,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -16278,7 +16202,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -16306,10 +16230,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -16329,7 +16253,7 @@
         <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
@@ -16349,7 +16273,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>22</v>
@@ -16398,7 +16322,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>36</v>
@@ -16430,7 +16354,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>36</v>
@@ -16462,7 +16386,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>36</v>
@@ -16491,7 +16415,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25">
@@ -16522,7 +16446,7 @@
         <v>19</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>3</v>
@@ -16542,7 +16466,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>21</v>
@@ -16562,7 +16486,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>22</v>
@@ -16643,7 +16567,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>36</v>
@@ -16675,7 +16599,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>36</v>
@@ -16704,7 +16628,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
@@ -16735,7 +16659,7 @@
         <v>26</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>3</v>
@@ -16752,10 +16676,10 @@
         <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>21</v>
@@ -16775,7 +16699,7 @@
         <v>19</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>22</v>
@@ -16824,7 +16748,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>36</v>
@@ -16856,7 +16780,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>36</v>
@@ -16888,7 +16812,7 @@
         <v>34</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>36</v>
@@ -16941,7 +16865,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -16972,7 +16896,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -16983,7 +16907,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -16995,10 +16919,10 @@
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -17006,10 +16930,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -17018,10 +16942,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>23</v>
@@ -17032,16 +16956,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>3</v>
@@ -17058,16 +16982,16 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
@@ -17081,16 +17005,16 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>23</v>
@@ -17142,7 +17066,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -17174,7 +17098,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -17206,7 +17130,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
@@ -17238,7 +17162,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>36</v>
@@ -17270,7 +17194,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
@@ -17319,7 +17243,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
@@ -17450,7 +17374,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
@@ -17460,7 +17384,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -17488,10 +17412,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -17508,10 +17432,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -17528,10 +17452,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>22</v>
@@ -17580,7 +17504,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
@@ -17612,7 +17536,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
@@ -17644,7 +17568,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
@@ -17673,7 +17597,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -17701,10 +17625,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -17721,10 +17645,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
@@ -17741,10 +17665,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>22</v>
@@ -17793,7 +17717,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>36</v>
@@ -17825,7 +17749,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>36</v>
@@ -17857,7 +17781,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>36</v>
@@ -18100,13 +18024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A998A2A8-F1B1-4026-9B6E-D2D31CC13EB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E98CEEC-8657-4A99-815B-2D3F4827EBD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4D43B3-8AE9-424B-9AA3-76ACECCF21C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD120536-5B08-498E-AC11-2395D1303737}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44C02B44-A968-4A99-AB20-0E835C0AF58A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6D6A23D-846C-4A61-B26E-0415AAB78A14}"/>
 </file>